--- a/Datos del programa.xlsx
+++ b/Datos del programa.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Prioridades actualizaciones" sheetId="1" r:id="rId1"/>
+    <sheet name="Pasos a seguir" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>rast_gps.dart</t>
   </si>
@@ -204,6 +205,33 @@
       </rPr>
       <t> - Tiempo real verdadero</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>listado de viajes por fecha</t>
+  </si>
+  <si>
+    <t>Celular</t>
+  </si>
+  <si>
+    <t>Servidor</t>
+  </si>
+  <si>
+    <t>Terminar la parte de la emision de viajes con paradas intermedias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">armar un detalle del viaje </t>
+  </si>
+  <si>
+    <t>armar recorridos x viaje</t>
+  </si>
+  <si>
+    <t>estado de viajes con numero de movil y viaje</t>
+  </si>
+  <si>
+    <t>sqlite (Cuando se queda sininternet guarda las ubicaciones)</t>
   </si>
 </sst>
 </file>
@@ -340,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -366,6 +394,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -792,4 +824,76 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" style="11"/>
+    <col min="3" max="3" width="54.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="61.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="11">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="11">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="11">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>